--- a/examples/expected/team-register-filled.xlsx
+++ b/examples/expected/team-register-filled.xlsx
@@ -84,7 +84,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>Учебный пример Docomator; все сведения вымышлены.</t>
+          <t>Учебный пример Оформлятор; все сведения вымышлены.</t>
         </is>
       </c>
     </row>
